--- a/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:53</t>
+    <t xml:space="preserve">2026-09-16 17:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
@@ -6,64 +6,108 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Nacionalidad" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Grupos" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Por_edad" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Diferencia_en_el_tiempo" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nacionalidad'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Diferencia_en_el_tiempo'!$A$1:$C$7</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t xml:space="preserve">grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mediana_de_las_regiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_de_los_residentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_de_quienes_se_movieron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Femenino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masculino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29 14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plot_migracion_sexo_2021_o_higgins.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movilidad interna: quienes se mueven, segun sexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de O'Higgins</t>
+  </si>
   <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">HOMBRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUJER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de creación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16 17:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIT - MDSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagen asociada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plot_migracion_sexo_2021_o_higgins.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movilidad interna según sexo (M_MOVINTERNA_a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidad territorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Región de O'Higgins (Regional)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tramo_de_edad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">residentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 a 4 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 a 29 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 a 59 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 a 14 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde 60 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veces</t>
   </si>
 </sst>
 </file>
@@ -428,9 +472,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="28.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,75 +489,49 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>2019</v>
+      <c r="A2" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.95</v>
+        <v>70.57</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.84</v>
+        <v>67.39</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>44.16</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2020</v>
+      <c r="A3" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.71</v>
+        <v>89.15</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5.46</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>7.06</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>6.22</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>8.05</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>6.3</v>
+        <v>84.17</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>55.84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C7"/>
+  <autoFilter ref="A1:E3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -528,62 +548,328 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>18403</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>99005</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>99.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>184339</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>74.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>59862</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>59.12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>87727</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>36.59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>19051</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>70.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>101150</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>114.85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>187140</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>106.19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>62599</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>57.27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>79929</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>46.24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D11"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:00</t>
+    <t xml:space="preserve">2026-09-29 18:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,7 +504,7 @@
         <v>70.57</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>67.39</v>
+        <v>67.4</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>49.97</v>

--- a/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:55</t>
+    <t xml:space="preserve">2026-10-01 19:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_sexo_2021_o_higgins.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:10</t>
+    <t xml:space="preserve">2026-10-05 04:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
